--- a/input/industry/Heat_levels.xlsx
+++ b/input/industry/Heat_levels.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CC3BDA-6A5D-4131-B8B6-68DB13B72D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844F426A-88B9-4235-89F9-802108BCEF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30600" yWindow="1065" windowWidth="21885" windowHeight="14730" xr2:uid="{14D76F3B-60B7-4511-B1B3-FDAA6825855D}"/>
+    <workbookView xWindow="6975" yWindow="2175" windowWidth="20175" windowHeight="13230" xr2:uid="{14D76F3B-60B7-4511-B1B3-FDAA6825855D}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>Industry</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t xml:space="preserve">Assumptions/Changes: </t>
+  </si>
+  <si>
+    <t>olefins</t>
+  </si>
+  <si>
+    <t>olefins_classic</t>
   </si>
 </sst>
 </file>
@@ -665,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -1226,19 +1232,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <f t="shared" ref="B14:B21" si="7">B13</f>
+        <f t="shared" ref="B14:B22" si="7">B13</f>
         <v>6.3355837966640189</v>
       </c>
       <c r="C14" s="4">
-        <f t="shared" ref="C14:C21" si="8">C13</f>
+        <f t="shared" ref="C14:C22" si="8">C13</f>
         <v>16.664416203335982</v>
       </c>
       <c r="D14">
-        <f t="shared" ref="D14:D21" si="9">D13</f>
+        <f t="shared" ref="D14:D22" si="9">D13</f>
         <v>11</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:E21" si="10">E13</f>
+        <f t="shared" ref="E14:E22" si="10">E13</f>
         <v>66</v>
       </c>
       <c r="G14" t="s">
@@ -1268,7 +1274,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="4">
-        <f t="shared" si="7"/>
+        <f>B14</f>
         <v>6.3355837966640189</v>
       </c>
       <c r="C15" s="4">
@@ -1307,10 +1313,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B16" s="4">
-        <f t="shared" si="7"/>
+        <f>B15</f>
         <v>6.3355837966640189</v>
       </c>
       <c r="C16" s="4">
@@ -1349,28 +1355,28 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="B17" s="4">
-        <f t="shared" si="7"/>
+        <f>B15</f>
         <v>6.3355837966640189</v>
       </c>
       <c r="C17" s="4">
-        <f t="shared" si="8"/>
+        <f>C15</f>
         <v>16.664416203335982</v>
       </c>
       <c r="D17">
-        <f t="shared" si="9"/>
+        <f>D15</f>
         <v>11</v>
       </c>
       <c r="E17">
-        <f t="shared" si="10"/>
+        <f>E15</f>
         <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="7"/>
@@ -1391,7 +1397,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="7"/>
@@ -1412,7 +1418,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="7"/>
@@ -1433,7 +1439,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="B21" s="4">
         <f t="shared" si="7"/>
@@ -1454,189 +1460,231 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="B22" s="4">
-        <f>B16</f>
+        <f t="shared" si="7"/>
         <v>6.3355837966640189</v>
       </c>
       <c r="C22" s="4">
-        <f>C16</f>
+        <f t="shared" si="8"/>
         <v>16.664416203335982</v>
       </c>
       <c r="D22">
-        <f>D16</f>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="E22">
-        <f>E16</f>
+        <f t="shared" si="10"/>
         <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="4">
+        <f>B21</f>
+        <v>6.3355837966640189</v>
+      </c>
+      <c r="C23" s="4">
+        <f>C21</f>
+        <v>16.664416203335982</v>
+      </c>
+      <c r="D23">
+        <f>D21</f>
+        <v>11</v>
+      </c>
+      <c r="E23">
+        <f>E21</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="4">
+        <f>B17</f>
+        <v>6.3355837966640189</v>
+      </c>
+      <c r="C24" s="4">
+        <f>C17</f>
+        <v>16.664416203335982</v>
+      </c>
+      <c r="D24">
+        <f>D17</f>
+        <v>11</v>
+      </c>
+      <c r="E24">
+        <f>E17</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B25" s="4">
         <f>H15*$O$4</f>
         <v>2.7152501985702937</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C25" s="4">
         <f>H15*$P$4+I15</f>
         <v>3.2847498014297063</v>
       </c>
-      <c r="D23">
+      <c r="D25">
         <f>J15</f>
         <v>19</v>
       </c>
-      <c r="E23">
+      <c r="E25">
         <f>SUM(K15:M15)</f>
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="4">
-        <f>B23</f>
+      <c r="B26" s="4">
+        <f>B25</f>
         <v>2.7152501985702937</v>
       </c>
-      <c r="C24" s="4">
-        <f t="shared" ref="C24:E24" si="11">C23</f>
+      <c r="C26" s="4">
+        <f t="shared" ref="C26:E26" si="11">C25</f>
         <v>3.2847498014297063</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D26" s="4">
         <f t="shared" si="11"/>
         <v>19</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E26" s="4">
         <f t="shared" si="11"/>
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="4">
-        <f>B24</f>
-        <v>2.7152501985702937</v>
-      </c>
-      <c r="C25" s="4">
-        <f t="shared" ref="C25" si="12">C24</f>
-        <v>3.2847498014297063</v>
-      </c>
-      <c r="D25" s="4">
-        <f t="shared" ref="D25" si="13">D24</f>
-        <v>19</v>
-      </c>
-      <c r="E25" s="4">
-        <f t="shared" ref="E25" si="14">E24</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="4">
-        <f>B23</f>
-        <v>2.7152501985702937</v>
-      </c>
-      <c r="C26" s="4">
-        <f>C23</f>
-        <v>3.2847498014297063</v>
-      </c>
-      <c r="D26">
-        <f>D23</f>
-        <v>19</v>
-      </c>
-      <c r="E26">
-        <f>E23</f>
-        <v>75</v>
-      </c>
-    </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="4">
+        <f>B26</f>
+        <v>2.7152501985702937</v>
+      </c>
+      <c r="C27" s="4">
+        <f t="shared" ref="C27" si="12">C26</f>
+        <v>3.2847498014297063</v>
+      </c>
+      <c r="D27" s="4">
+        <f t="shared" ref="D27" si="13">D26</f>
+        <v>19</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" ref="E27" si="14">E26</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="4">
+        <f>B25</f>
+        <v>2.7152501985702937</v>
+      </c>
+      <c r="C28" s="4">
+        <f>C25</f>
+        <v>3.2847498014297063</v>
+      </c>
+      <c r="D28">
+        <f>D25</f>
+        <v>19</v>
+      </c>
+      <c r="E28">
+        <f>E25</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B29" s="4">
         <f>H16*$O$4</f>
         <v>18.101667990468627</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C29" s="4">
         <f>H16*$P$4+I16</f>
         <v>5.8983320095313738</v>
       </c>
-      <c r="D27">
+      <c r="D29">
         <f>J16</f>
         <v>4</v>
       </c>
-      <c r="E27">
+      <c r="E29">
         <f>SUM(K16:M16)</f>
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="4">
-        <f>B27</f>
+      <c r="B30" s="4">
+        <f>B29</f>
         <v>18.101667990468627</v>
       </c>
-      <c r="C28" s="4">
-        <f t="shared" ref="C28:C30" si="15">C27</f>
+      <c r="C30" s="4">
+        <f t="shared" ref="C30:C32" si="15">C29</f>
         <v>5.8983320095313738</v>
       </c>
-      <c r="D28">
-        <f t="shared" ref="D28:D30" si="16">D27</f>
+      <c r="D30">
+        <f t="shared" ref="D30:D32" si="16">D29</f>
         <v>4</v>
       </c>
-      <c r="E28">
-        <f t="shared" ref="E28:E30" si="17">E27</f>
+      <c r="E30">
+        <f t="shared" ref="E30:E32" si="17">E29</f>
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="4">
-        <f t="shared" ref="B29:B30" si="18">B28</f>
+      <c r="B31" s="4">
+        <f t="shared" ref="B31:B32" si="18">B30</f>
         <v>18.101667990468627</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C31" s="4">
         <f t="shared" si="15"/>
         <v>5.8983320095313738</v>
       </c>
-      <c r="D29">
+      <c r="D31">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <f t="shared" si="17"/>
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B32" s="4">
         <f t="shared" si="18"/>
         <v>18.101667990468627</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C32" s="4">
         <f t="shared" si="15"/>
         <v>5.8983320095313738</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <f t="shared" si="17"/>
         <v>72</v>
       </c>
